--- a/#YNWA_anonymized.xlsx
+++ b/#YNWA_anonymized.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12829,7 +12829,7 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17830,7 +17830,7 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17873,7 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17915,7 +17915,7 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17957,7 +17957,7 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17999,7 +17999,7 @@
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23085,7 +23085,7 @@
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23123,7 +23123,7 @@
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23161,7 +23161,7 @@
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23202,7 +23202,7 @@
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23241,7 +23241,7 @@
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23320,7 +23320,7 @@
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
